--- a/juku-schedule/塾スケジュール雛形.xlsx
+++ b/juku-schedule/塾スケジュール雛形.xlsx
@@ -873,22 +873,22 @@
   </mergeCells>
   <dataValidations count="6">
     <dataValidation sqref="A3:A300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'設定'!$A$3:$A$100</formula1>
+      <formula1>"田中先生,佐藤先生,鈴木先生"</formula1>
     </dataValidation>
     <dataValidation sqref="B3:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'設定'!$B$3:$B$100</formula1>
+      <formula1>"生徒A,生徒B,生徒C"</formula1>
     </dataValidation>
     <dataValidation sqref="C3:C300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'設定'!$E$3:$E$9</formula1>
+      <formula1>"月,火,水,木,金,土,日"</formula1>
     </dataValidation>
     <dataValidation sqref="F3:F300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'設定'!$C$3:$C$100</formula1>
+      <formula1>"数学,英語,国語,理科,社会,物理,化学,英会話"</formula1>
     </dataValidation>
     <dataValidation sqref="G3:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'設定'!$D$3:$D$100</formula1>
+      <formula1>"教室,オンライン"</formula1>
     </dataValidation>
     <dataValidation sqref="H3:H300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'設定'!$F$3:$F$5</formula1>
+      <formula1>"毎週,A週,B週"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1053,19 +1053,19 @@
   </mergeCells>
   <dataValidations count="5">
     <dataValidation sqref="B3:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'設定'!$G$3:$G$5</formula1>
+      <formula1>"休講,振替,追加"</formula1>
     </dataValidation>
     <dataValidation sqref="C3:C300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'設定'!$A$3:$A$100</formula1>
+      <formula1>"田中先生,佐藤先生,鈴木先生"</formula1>
     </dataValidation>
     <dataValidation sqref="D3:D300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'設定'!$B$3:$B$100</formula1>
+      <formula1>"生徒A,生徒B,生徒C"</formula1>
     </dataValidation>
     <dataValidation sqref="E3:E300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'設定'!$C$3:$C$100</formula1>
+      <formula1>"数学,英語,国語,理科,社会,物理,化学,英会話"</formula1>
     </dataValidation>
     <dataValidation sqref="H3:H300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'設定'!$D$3:$D$100</formula1>
+      <formula1>"教室,オンライン"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
